--- a/ARREST_Import_Template_Final.xlsx
+++ b/ARREST_Import_Template_Final.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet sheetId="1" name="General Info" state="visible" r:id="rId4"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="181">
   <si>
     <t>linked_fir_dd_no</t>
   </si>
@@ -118,6 +118,9 @@
     <t>sections</t>
   </si>
   <si>
+    <t>crime_head</t>
+  </si>
+  <si>
     <t>Case Reference</t>
   </si>
   <si>
@@ -529,19 +532,7 @@
     <t>property_value</t>
   </si>
   <si>
-    <t>property_phone_number</t>
-  </si>
-  <si>
-    <t>phone_make</t>
-  </si>
-  <si>
-    <t>phone_model</t>
-  </si>
-  <si>
-    <t>phone_imei</t>
-  </si>
-  <si>
-    <t>phone_color</t>
+    <t>property_minor_category</t>
   </si>
   <si>
     <t>Property Details</t>
@@ -560,6 +551,9 @@
   </si>
   <si>
     <t>Property Value in inr</t>
+  </si>
+  <si>
+    <t>Type of property</t>
   </si>
   <si>
     <t>select: Vehicle, Mobile Phone, Cash, Jewellery, Electronics, Documents, Drugs, Arms, Others</t>
@@ -1025,7 +1019,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" ht="25" customHeight="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" ht="25.05" customHeight="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
@@ -1124,7 +1118,7 @@
     <col min="5" max="5" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" hidden="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1134,46 +1128,49 @@
       <c r="C1" t="s">
         <v>32</v>
       </c>
+      <c r="D1" t="s">
+        <v>33</v>
+      </c>
     </row>
-    <row r="2" ht="25" customHeight="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" ht="25.05" customHeight="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E2" s="2"/>
     </row>
     <row r="3" ht="19.95" customHeight="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" ht="16.05" customHeight="1" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -1217,150 +1214,150 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="N1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="O1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="P1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="T1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="U1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="W1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="X1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Y1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Z1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AA1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AB1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AC1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AE1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AF1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AG1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AI1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AJ1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AK1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AM1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AN1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AO1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AP1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AQ1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AR1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AS1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AT1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AU1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
-    <row r="2" ht="25" customHeight="1" spans="1:47" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" ht="25.05" customHeight="1" spans="1:47" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -1376,7 +1373,7 @@
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
       <c r="P2" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q2" s="2"/>
       <c r="R2" s="2"/>
@@ -1389,7 +1386,7 @@
       <c r="Y2" s="2"/>
       <c r="Z2" s="2"/>
       <c r="AA2" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AB2" s="2"/>
       <c r="AC2" s="2"/>
@@ -1403,7 +1400,7 @@
       <c r="AK2" s="2"/>
       <c r="AL2" s="2"/>
       <c r="AM2" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN2" s="2"/>
       <c r="AO2" s="2"/>
@@ -1416,285 +1413,285 @@
     </row>
     <row r="3" ht="19.95" customHeight="1" spans="1:47" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="T3" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="V3" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="W3" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="X3" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Y3" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Z3" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AA3" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AB3" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AC3" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AD3" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AE3" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AF3" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG3" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AH3" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AI3" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AJ3" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AK3" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AL3" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AM3" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AN3" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AO3" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AP3" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AQ3" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AR3" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AS3" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AT3" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AU3" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" ht="16.05" customHeight="1" spans="1:46" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M4" s="5" t="s">
         <v>26</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O4" s="5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P4" s="5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q4" s="5" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="R4" s="5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="S4" s="5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="T4" s="5" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="U4" s="5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="V4" s="5" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="W4" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="X4" s="5" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Y4" s="5" t="s">
         <v>17</v>
       </c>
       <c r="Z4" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="AA4" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="AB4" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="AC4" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="AD4" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="AE4" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="AF4" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="AG4" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="AH4" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="AI4" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="AJ4" s="5" t="s">
         <v>162</v>
-      </c>
-      <c r="AA4" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="AB4" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="AC4" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="AD4" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="AE4" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="AF4" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="AG4" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="AH4" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="AI4" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="AJ4" s="5" t="s">
-        <v>161</v>
       </c>
       <c r="AK4" s="5" t="s">
         <v>17</v>
       </c>
       <c r="AL4" s="5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AM4" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AN4" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AO4" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AP4" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AQ4" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AR4" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AS4" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AT4" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -1729,83 +1726,70 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F1" t="s">
-        <v>170</v>
-      </c>
-      <c r="G1" t="s">
         <v>171</v>
       </c>
-      <c r="H1" t="s">
+    </row>
+    <row r="2" ht="25.05" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="I1" t="s">
-        <v>173</v>
-      </c>
-      <c r="J1" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="2" ht="25" customHeight="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>175</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
     </row>
-    <row r="3" ht="19.95" customHeight="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="19.95" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
     </row>
     <row r="4" ht="16.05" customHeight="1" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B2:F2"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" sqref="B10:B1000">
